--- a/COSTOS BARATERO_actualizado.xlsx
+++ b/COSTOS BARATERO_actualizado.xlsx
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>7500533002760</t>
+          <t>ACEITE  OLIVA EXTRA VIRGEN MEMBERS MARK 1 LT</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>750222377259</t>
+          <t>ACEITE CAPULLO PURO DE CANOLA 750 ML</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>8410344401319</t>
+          <t>NO ENCONTRADO</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>11848455570</t>
+          <t>ACHIOTE KG</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>AJO</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>NO ENCONTRADO</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>502210100</t>
+          <t>ALUBIA CAMPIÑA 500GRS</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>501715000000</t>
+          <t>ANIS KG</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>750107130013</t>
+          <t>ARROZ INTEGRAL VALLE VERDE 900GRS</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>DESPENSA, ACEITE PATRONA 500 ML. AZUCAR ESTANDAR 1KG, LECHE ENTERA 1 LT, ATUN ANCLA EN AGUA 140 GR,PASTA FIDEO 200 GR, PASTA CODO 200 GR, FRIJOL NEGRO BUENO 900GR, ARROZ BUENO 900 GR</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>ATUN EN ACEITE NAIR 120 GR</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>681131755498</t>
+          <t>ATUN TUNY EN AGUA 140GRS</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>681131755498</t>
+          <t>ATUN TUNY EN AGUA 140GRS</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>750047802372</t>
+          <t>AVENA HOJUELAS INTEGRAL QUAKER OATS 800 GR</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>NO ENCONTRADO</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>7501059234123</t>
+          <t>CAFÉ SOLUBLE NESCAFÉ DECAF DESCAFEINADO 300 G</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>7501058616678</t>
+          <t>CEREAL GERBER ET1 ARROZ/AVENA</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>7501058616715</t>
+          <t>CEREAL GERBER ET1 ARROZ/AVENA</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>98000188400 WOONKIE</t>
+          <t>CHILE CHIPOTLE ADOBADO MEMBER'S MARK 2.8 KG</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>3363318</t>
+          <t>CHILES JALAPEÑOS LA COSTEÑA EN RAJAS 240 G</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>3043408</t>
+          <t>CHILES JALAPEÑOS LA COSTEÑA ENTEROS 780 G</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>3007367</t>
+          <t>CHORIZO SABORI DE SOYA VEGETARIANO 350G</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>LAVO MOLIDO</t>
+          <t>CLAVO MOLIDO PZA</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>COMINO ENTERO</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>COMINO ENTERO</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>CREMA DE CACAHUATE VF CON TROCITOS</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>EPAZOTE KG</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>FLOR DE JAMAICA 500GR</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>7501379119902</t>
+          <t>FRIJOL BAYO GRANEL</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>7500478043859</t>
+          <t>GALLETA MARIA CLASICA 122 GRS</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>GARBANZO KG</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>7501200481109</t>
+          <t>GRENETINA KNOX POLVO 4/SOBRES 28 G</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>7501069210759</t>
+          <t>HARINA DE ARROZ 3 ESTRELLAS 500 GR</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>LAUREL KG</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>7501379124395</t>
+          <t>LENTEJA CAMPIÑA 500GRS</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>980030752</t>
+          <t>MAYONESA MCCORMICK  468</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>MAYONESA MCCORMICK  468</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>MAYONESA MCCORMICK  468</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>MAYONESA MCCORMICK  468</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>MEJORANA</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>981014760 WOONKIE</t>
+          <t>MIEL DE ABEJA CARLOTA 500 GR</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>981014760 WOONKIE</t>
+          <t>MIEL DE ABEJA CARLOTA 300 GRS</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>7501017005369</t>
+          <t>NO ENCONTRADO</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>3621844</t>
+          <t>MOLE DOÑA MARIA VERDE 360 GRS</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>PEREJIL KG</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>PILONCILLO KG</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>3005633</t>
+          <t>PIMIENTA NEGRA SELECTO ENTERA 65G</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>981014248</t>
+          <t>PIMIENTA NEGRA MOLIDA MEMBER'S MARK 460GRS</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>POLVO PATA HORNEAR KOCI</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>TE DE MANZANILLA</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>TE DE NARANJO</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>TOMILLO KG</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>CHULETA DE CERDO AHUMADA</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>FALDA DE RES</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>LOMO DE CERDO</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>73131600</t>
+          <t>FILETE DE PESCADO MERO KG</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>POLLO ENTERO KG</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>NO ENCONTRADO</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>25204005</t>
+          <t>LECHE DESCREMADA DESLACTOSADA EN POLVO 500G DIF LA SUREÑA</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>25204005</t>
+          <t>LECHE DESCREMADA DESLACTOSADA EN POLVO 500G DIF LA SUREÑA</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>750053301567</t>
+          <t>MANTEQUILLA SIN SAL LYNCOTT 1KG</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>750053301567</t>
+          <t>MANTEQUILLA GLORIA S/SAL 90 GRS</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>750053301567</t>
+          <t>MANTEQUILLA GLORIA S/SAL 90 GRS</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>750053301567</t>
+          <t>MANTEQUILLA GLORIA S/SAL 90 GRS</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>CAÑA KG</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>MERMELADA CHABACANO SMUCKERS 510 GR</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>CIRUELA ROJA KG</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="F206" s="9" t="inlineStr">
         <is>
-          <t>50307035000</t>
+          <t>GUANABANA KG</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="F207" s="9" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>GUAYABA</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="F208" s="9" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>JICAMA KG</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>MAMEY KG</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>MANDARINA</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>MANZANA KG</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F218" s="9" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>NARANJA AGRIA</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>5030170000</t>
+          <t>PLATANO DOMINICO KG</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>PLATANO MACHO KG</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>SANDIA KG</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>50307037</t>
+          <t>TAMARINDO KG</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>50307000</t>
+          <t>TEJOCOTE KG</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>TUNA A GRANEL</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>UVA</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>15950403800</t>
+          <t>ACELGA KG</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>AGUACATE HASS</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>APIO</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>BETABEL KG</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>BROCOLI KG</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>CALABACITA ITALIANA KG</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>50406400</t>
+          <t>CAMOTE AMARILLO KG</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>CEBOLLA BLANCA</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>CEBOLLA CAMBRAY KG</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>CEBOLLA MORADA</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>CHICHARO LIMPIO</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>CHILE DE ARBOL</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>CHILE HABANERO</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>CHILE JALAPEÑO A GRANEL</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>50405632</t>
+          <t>CHILE POBLANO KG</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>CHILE SERRANO KG</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>CILANTRO MANOJO</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>5040230400000</t>
+          <t>COL BLANCA</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>COL MORADA KG</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>EJOTE KG</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>FLOR DE CALABAZA</t>
         </is>
       </c>
     </row>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>JITOMATE BOLA 6 PZA</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>LECHUGA ROMANA KG</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>LECHUGA OREJONA PZA</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>NOPAL KG</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>PAPA BLANCA</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>PEPINO KG</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>RABANO KG</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>ZANAHORIA KG</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>PAN CANAPE</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>TORTILLA DE MAIZ KG</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       <c r="E300" s="16"/>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO</t>
+          <t>TOSTADA SANISSIMO HORNEADA SALMA 360 GR</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>PIMIENTO MORRON AMARILLO</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>NARANJA AGRIA</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>NO ENCONTRADO</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>PICA FRESA</t>
         </is>
       </c>
     </row>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>MILANESA DE POLLO</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>PULPA BOLA DE RES</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>PULPA DE TAMARINDO</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>PAN DULCE</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>PULPA DE CERDO KG</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>CALABAZA CRIOLLA</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>CHILE HABANERO</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>LONGANIZA KG</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>PULPA DE MARACUYA</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>YUCA KG</t>
         </is>
       </c>
     </row>
